--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -1,41 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eyindia-my.sharepoint.com/personal/harshita_rastogi_in_ey_com/Documents/Documents/Training/practice/gold_price_alerts/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_56BDB35C1713BB85086837EDE99F8B23424D863D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{638B93F8-9B6A-4B84-9598-12ABE1E30955}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="gold_price" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="gold_price" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Gold Price (24K)</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -53,83 +67,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -417,72 +371,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="10.33203125" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Gold Price (24K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
         <v>46122</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>150881</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>46123</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>150881</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>46124</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>150881</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5">
         <v>150881</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6">
         <v>150881</v>
       </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -1,55 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eyindia-my.sharepoint.com/personal/harshita_rastogi_in_ey_com/Documents/Documents/Training/practice/gold_price_alerts/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_56BDB35C1713BB85086837EDE99F8B23424D863D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{638B93F8-9B6A-4B84-9598-12ABE1E30955}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gold_price" sheetId="1" r:id="rId1"/>
+    <sheet name="gold_price" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Gold Price (24K)</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -68,22 +48,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -371,69 +410,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Gold Price (24K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
         <v>46122</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>150881</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" s="1" t="n">
         <v>46123</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>150881</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" s="1" t="n">
         <v>46124</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>150881</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>150881</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>150881</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>152949</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -477,9 +477,6 @@
         <v>150881</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -490,6 +487,16 @@
         <v>152949</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>153305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -497,6 +497,16 @@
         <v>153305</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>151358</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -507,6 +507,16 @@
         <v>151358</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>152002</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -517,6 +517,16 @@
         <v>152002</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>152155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -527,6 +527,16 @@
         <v>152155</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>152250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -537,6 +537,16 @@
         <v>152250</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>151189</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -547,6 +547,16 @@
         <v>151189</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>150664</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -557,6 +557,16 @@
         <v>150664</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>151495</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -567,6 +567,16 @@
         <v>151495</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>149557</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -577,6 +577,16 @@
         <v>149557</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>149557</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -587,6 +587,16 @@
         <v>149557</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>148821</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -597,6 +597,16 @@
         <v>148821</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>148652</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -607,6 +607,16 @@
         <v>148652</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>148357</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -617,6 +617,16 @@
         <v>148357</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>147557</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -627,6 +627,16 @@
         <v>147557</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>150636</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -637,6 +637,16 @@
         <v>150636</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>151237</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -647,6 +647,16 @@
         <v>151237</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>151140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -657,6 +657,16 @@
         <v>151140</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>150277</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -667,6 +667,16 @@
         <v>150277</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>151954</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -677,6 +677,16 @@
         <v>151954</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>160411</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -687,6 +687,16 @@
         <v>160411</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>161349</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -697,6 +697,16 @@
         <v>161349</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>158159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -707,6 +707,16 @@
         <v>158159</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>157821</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -717,6 +717,16 @@
         <v>157821</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>158907</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -727,6 +727,16 @@
         <v>158907</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>157961</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -737,6 +737,16 @@
         <v>157961</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>158947</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -747,6 +747,16 @@
         <v>158947</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>158354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -757,6 +757,16 @@
         <v>158354</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>158622</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -767,6 +767,16 @@
         <v>158622</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>157040</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -777,6 +777,16 @@
         <v>157040</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>157043</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -787,6 +787,16 @@
         <v>157043</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>155599</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -797,6 +797,16 @@
         <v>155599</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>156296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -807,6 +807,16 @@
         <v>156296</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>155264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -817,6 +817,16 @@
         <v>155264</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>155581</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -827,6 +827,16 @@
         <v>155581</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>154190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -837,6 +837,16 @@
         <v>154190</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>150768</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -847,6 +847,16 @@
         <v>150768</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>152584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B47"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -857,6 +857,16 @@
         <v>152584</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>148429</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B48"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -867,6 +867,16 @@
         <v>148429</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>145584</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -877,6 +877,16 @@
         <v>145584</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>147609</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -887,6 +887,16 @@
         <v>147609</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>150169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -897,6 +897,16 @@
         <v>150169</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>150094</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -907,6 +907,16 @@
         <v>150094</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>150105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -917,6 +917,16 @@
         <v>150105</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>149332</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -927,6 +927,16 @@
         <v>149332</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>144941</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -937,6 +937,16 @@
         <v>144941</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>146664</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -947,6 +947,16 @@
         <v>146664</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>144788</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -957,6 +957,16 @@
         <v>144788</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>143890</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -967,6 +967,16 @@
         <v>143890</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>140022</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -977,6 +977,16 @@
         <v>140022</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>141911</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -987,6 +987,16 @@
         <v>141911</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>140382</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -997,6 +997,16 @@
         <v>140382</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>139434</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1007,6 +1007,16 @@
         <v>139434</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>143340</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1017,6 +1017,16 @@
         <v>143340</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>146107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1027,6 +1027,16 @@
         <v>146107</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>145512</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B65"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1037,6 +1037,16 @@
         <v>145512</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>144141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1047,6 +1047,16 @@
         <v>144141</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>144260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1057,6 +1057,16 @@
         <v>144260</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>143372</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1067,6 +1067,16 @@
         <v>143372</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>143815</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1077,6 +1077,16 @@
         <v>143815</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>142289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1087,6 +1087,16 @@
         <v>142289</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>141712</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1097,6 +1097,16 @@
         <v>141712</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>141770</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1107,6 +1107,16 @@
         <v>141770</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>141713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1117,6 +1117,16 @@
         <v>141713</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>141264</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1127,6 +1127,16 @@
         <v>141264</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>141915</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1137,6 +1137,16 @@
         <v>141915</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>143404</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1147,6 +1147,16 @@
         <v>143404</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>145440</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B77"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1157,6 +1157,16 @@
         <v>145440</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>145557</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1167,6 +1167,16 @@
         <v>145557</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>142757</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1177,6 +1177,16 @@
         <v>142757</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>144532</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1187,6 +1187,16 @@
         <v>144532</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>142559</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1197,6 +1197,16 @@
         <v>142559</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>142469</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B82"/>
+  <dimension ref="A1:B83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1207,6 +1207,16 @@
         <v>142469</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>142401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1217,6 +1217,16 @@
         <v>142401</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>143329</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1227,6 +1227,16 @@
         <v>143329</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>142863</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1237,6 +1237,16 @@
         <v>142863</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>142938</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B86"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1247,6 +1247,16 @@
         <v>142938</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>145577</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1257,6 +1257,16 @@
         <v>145577</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>148361</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1267,6 +1267,16 @@
         <v>148361</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>149020</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1277,6 +1277,16 @@
         <v>149020</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>151061</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1287,6 +1287,16 @@
         <v>151061</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>152490</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1297,6 +1297,16 @@
         <v>152490</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>152961</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1307,6 +1307,16 @@
         <v>152961</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>152447</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1317,6 +1317,16 @@
         <v>152447</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>151493</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B94"/>
+  <dimension ref="A1:B95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1327,6 +1327,16 @@
         <v>151493</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>154066</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B95"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1337,6 +1337,16 @@
         <v>154066</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>154162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1347,6 +1347,16 @@
         <v>154162</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>152884</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1357,6 +1357,16 @@
         <v>152884</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>157387</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B98"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1367,6 +1367,16 @@
         <v>157387</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>159499</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1377,6 +1377,16 @@
         <v>159499</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>162603</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1387,6 +1387,16 @@
         <v>162603</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>162344</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1397,6 +1397,16 @@
         <v>162344</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>161431</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1407,6 +1407,16 @@
         <v>161431</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>158477</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B103"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1417,6 +1417,16 @@
         <v>158477</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>158226</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1427,6 +1427,16 @@
         <v>158226</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>155125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B105"/>
+  <dimension ref="A1:B106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1437,6 +1437,16 @@
         <v>155125</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>154798</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1447,6 +1447,16 @@
         <v>154798</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>151328</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1457,6 +1457,16 @@
         <v>151328</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>153733</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/gold_price_tracking.xlsx
+++ b/gold_price_tracking.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B108"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.33203125" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -1467,6 +1467,16 @@
         <v>153733</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>154908</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
